--- a/qa_knowledge.xlsx
+++ b/qa_knowledge.xlsx
@@ -397,12 +397,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D16"/>
+  <dimension ref="A1:D35"/>
   <cols>
-    <col min="1" max="1" width="12.83203125" customWidth="1"/>
-    <col min="2" max="2" width="35.83203125" customWidth="1"/>
-    <col min="3" max="3" width="60.83203125" customWidth="1"/>
-    <col min="4" max="4" width="25.83203125" customWidth="1"/>
+    <col min="1" max="1" width="14.83203125" customWidth="1"/>
+    <col min="2" max="2" width="38.83203125" customWidth="1"/>
+    <col min="3" max="3" width="65.83203125" customWidth="1"/>
+    <col min="4" max="4" width="30.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -447,15 +447,19 @@
         <v>冷凍,管理,温度,-18</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" xml:space="preserve">
       <c r="A4" t="str">
         <v>温度管理</v>
       </c>
       <c r="B4" t="str">
         <v>温度異常が発生したときの対応手順は？</v>
       </c>
-      <c r="C4" t="str">
-        <v>①すぐに管理責任者（内線:201）に報告 ②該当区画の商品を別の適温エリアに移動 ③温度記録に異常内容を記載 ④修理依頼は設備管理部（内線:305）へ連絡 ⑤移動した商品は品質確認後に販売可否を判断します。</v>
+      <c r="C4" t="str" xml:space="preserve">
+        <v xml:space="preserve">①すぐに管理責任者（内線:201）に報告
+②該当区画の商品を別の適温エリアに移動
+③温度記録に異常内容を記載
+④修理依頼は設備管理部（内線:305）へ連絡
+⑤移動した商品は品質確認後に販売可否を判断します。</v>
       </c>
       <c r="D4" t="str">
         <v>温度異常,対応,緊急</v>
@@ -463,175 +467,509 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>入出荷</v>
+        <v>温度管理</v>
       </c>
       <c r="B5" t="str">
-        <v>入荷検品の手順を教えてください</v>
+        <v>温度チェックはいつ・誰が行いますか？</v>
       </c>
       <c r="C5" t="str">
-        <v>①納品伝票と現物の品番・数量を照合 ②賞味期限・消費期限の確認（先入れ先出しルール適用）③外装の破損・汚損チェック ④冷蔵・冷凍品は受取後すぐに温度確認して入庫 ⑤検品完了後、入荷システムに登録します。</v>
+        <v>温度チェックは各シフトリーダーが担当します。チェック時間は午前8時・正午・午後4時・午後8時の1日4回です。記録用紙に記入後、月末にまとめて品質管理部へ提出してください。</v>
       </c>
       <c r="D5" t="str">
-        <v>入荷,検品,手順</v>
+        <v>温度チェック,記録,シフト</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>入出荷</v>
+        <v>温度管理</v>
       </c>
       <c r="B6" t="str">
-        <v>先入れ先出し（FIFO）の原則とは何ですか？</v>
+        <v>ドライ品（常温）の保管条件は？</v>
       </c>
       <c r="C6" t="str">
-        <v>先に入荷した商品を先に出荷するルールです。新しい在庫を棚の後ろに補充し、古い在庫を前に出してください。賞味期限が近いものが常に手前になるよう整理してください。</v>
+        <v>常温保管品は15〜25℃、湿度70%以下の環境で保管してください。直射日光・高温多湿を避け、床から10cm以上離したパレット上に置いてください。</v>
       </c>
       <c r="D6" t="str">
-        <v>FIFO,先入れ先出し,在庫</v>
-      </c>
-    </row>
-    <row r="7">
+        <v>ドライ,常温,保管,湿度</v>
+      </c>
+    </row>
+    <row r="7" xml:space="preserve">
       <c r="A7" t="str">
         <v>入出荷</v>
       </c>
       <c r="B7" t="str">
-        <v>出荷前の最終確認項目は？</v>
-      </c>
-      <c r="C7" t="str">
-        <v>①ピッキングリストと現物の一致確認 ②賞味期限の再確認（当日出荷不可品がないか）③温度管理品の保冷資材確認 ④配送先ラベルの貼付確認 ⑤荷崩れ防止のラップ巻き確認。</v>
+        <v>入荷検品の手順を教えてください</v>
+      </c>
+      <c r="C7" t="str" xml:space="preserve">
+        <v xml:space="preserve">①納品伝票と現物の品番・数量を照合
+②賞味期限・消費期限の確認（先入れ先出しルール適用）
+③外装の破損・汚損チェック
+④冷蔵・冷凍品は受取後すぐに温度確認して入庫
+⑤検品完了後、入荷システムに登録します。</v>
       </c>
       <c r="D7" t="str">
-        <v>出荷,確認,ピッキング</v>
+        <v>入荷,検品,手順</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>安全・衛生</v>
+        <v>入出荷</v>
       </c>
       <c r="B8" t="str">
-        <v>作業前の衛生チェック項目は？</v>
+        <v>先入れ先出し（FIFO）の原則とは何ですか？</v>
       </c>
       <c r="C8" t="str">
-        <v>①手洗い・アルコール消毒（30秒以上）②爪を短く切っているか確認 ③清潔な作業着・帽子・手袋の着用 ④体調不良（発熱・下痢・嘔吐）の場合は作業不可・報告 ⑤アクセサリー・時計の取り外しを確認してください。</v>
+        <v>先に入荷した商品を先に出荷するルールです。新しい在庫を棚の後ろに補充し、古い在庫を前に出してください。賞味期限が近いものが常に手前になるよう整理してください。</v>
       </c>
       <c r="D8" t="str">
-        <v>衛生,手洗い,作業前</v>
-      </c>
-    </row>
-    <row r="9">
+        <v>FIFO,先入れ先出し,在庫</v>
+      </c>
+    </row>
+    <row r="9" xml:space="preserve">
       <c r="A9" t="str">
-        <v>安全・衛生</v>
+        <v>入出荷</v>
       </c>
       <c r="B9" t="str">
-        <v>フォークリフトの安全確認事項を教えてください</v>
-      </c>
-      <c r="C9" t="str">
-        <v>①始業前点検（タイヤ・油圧・ライト・ホーン）②フォーク爪の高さは走行時15cm以下 ③歩行者優先エリアでの徐行（5km/h以下）④積荷は視界を妨げない高さで運搬 ⑤免許保有者のみ運転可。無免許運転は厳禁です。</v>
+        <v>出荷前の最終確認項目は？</v>
+      </c>
+      <c r="C9" t="str" xml:space="preserve">
+        <v xml:space="preserve">①ピッキングリストと現物の一致確認
+②賞味期限の再確認（当日出荷不可品がないか）
+③温度管理品の保冷資材確認
+④配送先ラベルの貼付確認
+⑤荷崩れ防止のラップ巻き確認。</v>
       </c>
       <c r="D9" t="str">
-        <v>フォークリフト,安全,点検</v>
-      </c>
-    </row>
-    <row r="10">
+        <v>出荷,確認,ピッキング</v>
+      </c>
+    </row>
+    <row r="10" xml:space="preserve">
       <c r="A10" t="str">
-        <v>安全・衛生</v>
+        <v>入出荷</v>
       </c>
       <c r="B10" t="str">
-        <v>食品アレルゲン管理の注意点は？</v>
-      </c>
-      <c r="C10" t="str">
-        <v>①アレルゲン対応商品（特定7品目）は専用棚で保管 ②作業ライン・器具の共用禁止 ③アレルゲン情報の表示確認を必ず実施 ④不明点は食品表示担当（内線:208）に確認してください。</v>
+        <v>納品ドライバーへの対応ルールは？</v>
+      </c>
+      <c r="C10" t="str" xml:space="preserve">
+        <v xml:space="preserve">①入構時に受付票への記入を依頼
+②荷物は必ず検品してから受け取る（無検品受領禁止）
+③車両ナンバーを台帳に記録
+④荷降ろし中は安全のため荷台周辺に立ち入らない
+⑤帰還前に受領書にサインして渡してください。</v>
       </c>
       <c r="D10" t="str">
-        <v>アレルゲン,管理,特定7品目</v>
+        <v>ドライバー,納品,受領</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>システム</v>
+        <v>入出荷</v>
       </c>
       <c r="B11" t="str">
+        <v>緊急入荷が発生した場合の対応は？</v>
+      </c>
+      <c r="C11" t="str">
+        <v>通常の検品手順を省略することはできません。緊急の場合でも最低限の数量確認と温度確認を実施してください。担当者が不在の場合は管理責任者（内線:201）に連絡を取ってから受領してください。</v>
+      </c>
+      <c r="D11" t="str">
+        <v>緊急入荷,対応</v>
+      </c>
+    </row>
+    <row r="12" xml:space="preserve">
+      <c r="A12" t="str">
+        <v>安全・衛生</v>
+      </c>
+      <c r="B12" t="str">
+        <v>作業前の衛生チェック項目は？</v>
+      </c>
+      <c r="C12" t="str" xml:space="preserve">
+        <v xml:space="preserve">①手洗い・アルコール消毒（30秒以上）
+②爪を短く切っているか確認
+③清潔な作業着・帽子・手袋の着用
+④体調不良（発熱・下痢・嘔吐）の場合は作業不可・報告
+⑤アクセサリー・時計の取り外しを確認してください。</v>
+      </c>
+      <c r="D12" t="str">
+        <v>衛生,手洗い,作業前</v>
+      </c>
+    </row>
+    <row r="13" xml:space="preserve">
+      <c r="A13" t="str">
+        <v>安全・衛生</v>
+      </c>
+      <c r="B13" t="str">
+        <v>フォークリフトの安全確認事項を教えてください</v>
+      </c>
+      <c r="C13" t="str" xml:space="preserve">
+        <v xml:space="preserve">①始業前点検（タイヤ・油圧・ライト・ホーン）
+②フォーク爪の高さは走行時15cm以下
+③歩行者優先エリアでの徐行（5km/h以下）
+④積荷は視界を妨げない高さで運搬
+⑤免許保有者のみ運転可（無免許運転は厳禁）</v>
+      </c>
+      <c r="D13" t="str">
+        <v>フォークリフト,安全,点検</v>
+      </c>
+    </row>
+    <row r="14" xml:space="preserve">
+      <c r="A14" t="str">
+        <v>安全・衛生</v>
+      </c>
+      <c r="B14" t="str">
+        <v>食品アレルゲン管理の注意点は？</v>
+      </c>
+      <c r="C14" t="str" xml:space="preserve">
+        <v xml:space="preserve">①特定7品目（小麦・乳・卵・えび・かに・そば・落花生）は専用棚で保管
+②作業ライン・器具の共用禁止
+③アレルゲン情報の表示確認を必ず実施
+④不明点は食品表示担当（内線:208）に確認してください。</v>
+      </c>
+      <c r="D14" t="str">
+        <v>アレルゲン,管理,特定7品目</v>
+      </c>
+    </row>
+    <row r="15" xml:space="preserve">
+      <c r="A15" t="str">
+        <v>安全・衛生</v>
+      </c>
+      <c r="B15" t="str">
+        <v>害虫・異物混入を防ぐための対策は？</v>
+      </c>
+      <c r="C15" t="str" xml:space="preserve">
+        <v xml:space="preserve">①入口の防虫カーテン・エアカーテンを常時稼働
+②段ボールは倉庫内に放置しない（虫の住処になります）
+③定期的な床清掃と排水口の確認
+④異物を発見した場合は即座に品質管理部（内線:206）へ報告してください。</v>
+      </c>
+      <c r="D15" t="str">
+        <v>害虫,異物,混入,防止</v>
+      </c>
+    </row>
+    <row r="16" xml:space="preserve">
+      <c r="A16" t="str">
+        <v>安全・衛生</v>
+      </c>
+      <c r="B16" t="str">
+        <v>重量物を持ち上げるときの正しい姿勢は？</v>
+      </c>
+      <c r="C16" t="str" xml:space="preserve">
+        <v xml:space="preserve">①荷物の前にしゃがみ、背筋を伸ばす
+②膝を使って持ち上げる（腰だけで持ち上げない）
+③20kg以上は2人作業が基本
+④腰痛が続く場合は総務部へ相談し、医師の診断を受けてください。</v>
+      </c>
+      <c r="D16" t="str">
+        <v>重量物,腰痛,持ち上げ,姿勢</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>在庫管理</v>
+      </c>
+      <c r="B17" t="str">
         <v>在庫管理システムへのログイン方法は？</v>
       </c>
-      <c r="C11" t="str">
-        <v>社内ネットワーク経由でhttp://wms.logistics.localにアクセスしてください。ユーザーIDは社員番号、初期パスワードは「Taisho@000」です。初回ログイン後に必ずパスワードを変更してください。問題がある場合はITサポート（内線:400）へ連絡を。</v>
-      </c>
-      <c r="D11" t="str">
-        <v>システム,ログイン,WMS</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>システム</v>
-      </c>
-      <c r="B12" t="str">
+      <c r="C17" t="str">
+        <v>社内ネットワーク経由でhttp://wms.logistics.localにアクセスしてください。ユーザーIDは社員番号、初期パスワードは「Taisho@000」です。初回ログイン後は必ずパスワードを変更してください。問題がある場合はITサポート（内線:400）へ連絡を。</v>
+      </c>
+      <c r="D17" t="str">
+        <v>システム,ログイン,WMS,パスワード</v>
+      </c>
+    </row>
+    <row r="18" xml:space="preserve">
+      <c r="A18" t="str">
+        <v>在庫管理</v>
+      </c>
+      <c r="B18" t="str">
         <v>ピッキングリストの印刷方法を教えてください</v>
       </c>
-      <c r="C12" t="str">
-        <v>①在庫管理システムにログイン ②「出荷管理」→「ピッキングリスト」を選択 ③対象日・配送先を指定 ④「印刷」ボタンを押してプリンタ（事務所プリンタ3番）で出力してください。</v>
-      </c>
-      <c r="D12" t="str">
+      <c r="C18" t="str" xml:space="preserve">
+        <v xml:space="preserve">①在庫管理システムにログイン
+②「出荷管理」→「ピッキングリスト」を選択
+③対象日・配送先を指定
+④「印刷」ボタンを押してプリンタ（事務所プリンタ3番）で出力してください。</v>
+      </c>
+      <c r="D18" t="str">
         <v>ピッキング,印刷,システム</v>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="str">
+    <row r="19">
+      <c r="A19" t="str">
+        <v>在庫管理</v>
+      </c>
+      <c r="B19" t="str">
+        <v>在庫の棚卸しはどのくらいの頻度で行いますか？</v>
+      </c>
+      <c r="C19" t="str">
+        <v>月次棚卸しを毎月最終営業日の閉業後に実施します。年1回（3月末）に全品目の精密棚卸しを行います。差異が発生した場合は翌営業日中に在庫管理担当（内線:203）へ報告してください。</v>
+      </c>
+      <c r="D19" t="str">
+        <v>棚卸し,在庫,頻度,月次</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>在庫管理</v>
+      </c>
+      <c r="B20" t="str">
+        <v>賞味期限が近い商品の管理方法は？</v>
+      </c>
+      <c r="C20" t="str">
+        <v>期限30日前：「要注意」ラベルを貼付し、棚の最前列へ移動。期限14日前：品質管理部（内線:206）へ報告し、値引き販売または廃棄の判断を仰ぐ。期限切れ商品は絶対に出荷禁止です。</v>
+      </c>
+      <c r="D20" t="str">
+        <v>賞味期限,期限管理,ラベル</v>
+      </c>
+    </row>
+    <row r="21" xml:space="preserve">
+      <c r="A21" t="str">
+        <v>在庫管理</v>
+      </c>
+      <c r="B21" t="str">
+        <v>商品の返品処理手順を教えてください</v>
+      </c>
+      <c r="C21" t="str" xml:space="preserve">
+        <v xml:space="preserve">①返品伝票を受け取り内容を確認
+②商品の状態（外装・品質）を写真撮影
+③「返品受付台帳」に記録
+④冷蔵・冷凍品は一時的に隔離エリアで保管
+⑤仕入先への返品連絡は営業担当（内線:202）が実施します。</v>
+      </c>
+      <c r="D21" t="str">
+        <v>返品,処理,手順</v>
+      </c>
+    </row>
+    <row r="22" xml:space="preserve">
+      <c r="A22" t="str">
+        <v>緊急対応</v>
+      </c>
+      <c r="B22" t="str">
+        <v>火災発生時の対応手順は？</v>
+      </c>
+      <c r="C22" t="str" xml:space="preserve">
+        <v xml:space="preserve">①大声で「火事だ！」と周囲に知らせる
+②火災報知器を押す
+③消防署（119）・施設管理（内線:300）に通報
+④初期消火は消火器で対応（無理は禁物）
+⑤避難経路に従い全員退避
+⑥点呼場所：正門前駐車場</v>
+      </c>
+      <c r="D22" t="str">
+        <v>火災,緊急,避難,119</v>
+      </c>
+    </row>
+    <row r="23" xml:space="preserve">
+      <c r="A23" t="str">
+        <v>緊急対応</v>
+      </c>
+      <c r="B23" t="str">
+        <v>商品クレームが入った場合の対処方法は？</v>
+      </c>
+      <c r="C23" t="str" xml:space="preserve">
+        <v xml:space="preserve">①クレーム内容を詳細に記録（日時・商品名・ロット番号・内容）
+②当該商品の在庫を確保・隔離
+③品質管理担当（内線:206）に即時報告
+④お客様には誠意をもって対応し、回答期限を伝える
+⑤原因調査・再発防止策を報告書にまとめてください。</v>
+      </c>
+      <c r="D23" t="str">
+        <v>クレーム,対応,品質</v>
+      </c>
+    </row>
+    <row r="24" xml:space="preserve">
+      <c r="A24" t="str">
+        <v>緊急対応</v>
+      </c>
+      <c r="B24" t="str">
+        <v>停電時の食品管理はどうすればいいですか？</v>
+      </c>
+      <c r="C24" t="str" xml:space="preserve">
+        <v xml:space="preserve">①冷蔵庫・冷凍庫の扉を開けないこと
+②設備管理（内線:305）と管理責任者に即報告
+③2時間以内に電力が回復しない場合は代替保管先（第2倉庫：TEL 03-XXXX-1234）と協議
+④温度記録を継続し、品質判断は品質管理部が行います。</v>
+      </c>
+      <c r="D24" t="str">
+        <v>停電,緊急,冷蔵庫,対応</v>
+      </c>
+    </row>
+    <row r="25" xml:space="preserve">
+      <c r="A25" t="str">
+        <v>緊急対応</v>
+      </c>
+      <c r="B25" t="str">
+        <v>従業員が怪我をした場合の応急処置と報告は？</v>
+      </c>
+      <c r="C25" t="str" xml:space="preserve">
+        <v xml:space="preserve">①応急処置を施し、必要であれば救急車（119）を呼ぶ
+②管理責任者（内線:201）に即報告
+③「労働災害報告書」を24時間以内に総務部（内線:210）へ提出
+④軽傷でも必ず記録に残すこと（後日悪化する場合あり）</v>
+      </c>
+      <c r="D25" t="str">
+        <v>怪我,労災,応急処置,119</v>
+      </c>
+    </row>
+    <row r="26" xml:space="preserve">
+      <c r="A26" t="str">
+        <v>緊急対応</v>
+      </c>
+      <c r="B26" t="str">
+        <v>異臭・異味のある商品を発見した場合は？</v>
+      </c>
+      <c r="C26" t="str" xml:space="preserve">
+        <v xml:space="preserve">①該当商品を隔離し、他の商品と混ざらないようにする
+②品質管理部（内線:206）に即報告
+③ロット番号・入荷日・保管場所を記録
+④絶対に出荷しないこと。廃棄処分は品質管理部の指示に従ってください。</v>
+      </c>
+      <c r="D26" t="str">
+        <v>異臭,異味,品質異常,廃棄</v>
+      </c>
+    </row>
+    <row r="27" xml:space="preserve">
+      <c r="A27" t="str">
         <v>業務ルール</v>
       </c>
-      <c r="B13" t="str">
+      <c r="B27" t="str">
         <v>時間外作業が発生した場合の申請方法は？</v>
       </c>
-      <c r="C13" t="str">
-        <v>時間外作業は事前に直属上長の承認が必要です。①勤怠管理システムで「時間外申請」を選択 ②作業理由・予定時間を入力 ③上長承認後に作業開始。緊急の場合は上長に直接連絡してから事後申請してください。</v>
-      </c>
-      <c r="D13" t="str">
+      <c r="C27" t="str" xml:space="preserve">
+        <v xml:space="preserve">時間外作業は事前に直属上長の承認が必要です。①勤怠管理システムで「時間外申請」を選択
+②作業理由・予定時間を入力
+③上長承認後に作業開始。緊急の場合は上長に直接連絡してから事後申請してください。</v>
+      </c>
+      <c r="D27" t="str">
         <v>時間外,残業,申請</v>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="str">
-        <v>緊急対応</v>
-      </c>
-      <c r="B14" t="str">
-        <v>火災発生時の対応手順は？</v>
-      </c>
-      <c r="C14" t="str">
-        <v>①大声で「火事だ！」と周囲に知らせる ②火災報知器を押す ③消防署（119）・施設管理（内線:300）に通報 ④初期消火は消火器で対応（無理は禁物）⑤避難経路に従い全員退避 ⑥点呼場所：正門前駐車場。</v>
-      </c>
-      <c r="D14" t="str">
-        <v>火災,緊急,避難,119</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="str">
-        <v>緊急対応</v>
-      </c>
-      <c r="B15" t="str">
-        <v>商品クレームが入った場合の対処方法は？</v>
-      </c>
-      <c r="C15" t="str">
-        <v>①クレーム内容を詳細に記録（日時・商品名・ロット番号・内容）②当該商品の在庫を確保・隔離 ③品質管理担当（内線:206）に即時報告 ④お客様には誠意をもって対応し、回答期限を伝える ⑤原因調査・再発防止策を報告書にまとめてください。</v>
-      </c>
-      <c r="D15" t="str">
-        <v>クレーム,対応,品質</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="str">
-        <v>緊急対応</v>
-      </c>
-      <c r="B16" t="str">
-        <v>停電時の食品管理はどうすればいいですか？</v>
-      </c>
-      <c r="C16" t="str">
-        <v>①冷蔵庫・冷凍庫の扉を開けないこと ②設備管理（内線:305）と管理責任者に即報告 ③2時間以内に電力が回復しない場合は代替保管先（第2倉庫：電話:03-XXXX-1234）と協議 ④温度記録を継続し、品質判断は品質管理部が行います。</v>
-      </c>
-      <c r="D16" t="str">
-        <v>停電,緊急,冷蔵庫,対応</v>
+    <row r="28">
+      <c r="A28" t="str">
+        <v>業務ルール</v>
+      </c>
+      <c r="B28" t="str">
+        <v>休憩時間のルールを教えてください</v>
+      </c>
+      <c r="C28" t="str">
+        <v>1日8時間勤務の場合、法定休憩は1時間です。午前・午後それぞれ15分の小休憩と、正午前後に45分の昼食休憩が基本です。休憩中は必ず食堂または休憩室を使用し、作業エリアでの飲食は禁止です。</v>
+      </c>
+      <c r="D28" t="str">
+        <v>休憩,昼食,ルール</v>
+      </c>
+    </row>
+    <row r="29" xml:space="preserve">
+      <c r="A29" t="str">
+        <v>業務ルール</v>
+      </c>
+      <c r="B29" t="str">
+        <v>制服・安全装備の着用ルールは？</v>
+      </c>
+      <c r="C29" t="str" xml:space="preserve">
+        <v xml:space="preserve">①作業中は常に制服・安全靴・帽子を着用
+②冷凍エリア作業時は防寒具（会社貸与）を必ず着用
+③安全靴の交換は年2回（4月・10月）に申請可能
+④私服での作業エリア立ち入りは禁止です。</v>
+      </c>
+      <c r="D29" t="str">
+        <v>制服,安全靴,服装,防寒</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="str">
+        <v>業務ルール</v>
+      </c>
+      <c r="B30" t="str">
+        <v>携帯電話・スマートフォンの使用ルールは？</v>
+      </c>
+      <c r="C30" t="str">
+        <v>作業エリア内での私的な携帯電話使用は禁止です。緊急連絡が必要な場合は休憩室または事務所で使用してください。業務用タブレットの使用は業務目的に限定します。</v>
+      </c>
+      <c r="D30" t="str">
+        <v>携帯電話,スマートフォン,使用禁止</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="str">
+        <v>業務ルール</v>
+      </c>
+      <c r="B31" t="str">
+        <v>有給休暇の申請方法は？</v>
+      </c>
+      <c r="C31" t="str">
+        <v>有給休暇は希望日の1週間前までに勤怠管理システムで申請してください。繁忙期（12月・3月）は調整が必要な場合があります。当日急な取得は電話で直属上長に連絡後、事後システム申請としてください。</v>
+      </c>
+      <c r="D31" t="str">
+        <v>有給,休暇,申請</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="str">
+        <v>施設・設備</v>
+      </c>
+      <c r="B32" t="str">
+        <v>各エリアの内線番号一覧を教えてください</v>
+      </c>
+      <c r="C32" t="str">
+        <v>管理責任者:201 / 営業担当:202 / 在庫管理:203 / 品質管理:206 / 食品表示担当:208 / 総務部:210 / 施設管理:300 / 設備管理:305 / ITサポート:400 / 警備室:500</v>
+      </c>
+      <c r="D32" t="str">
+        <v>内線,連絡先,電話</v>
+      </c>
+    </row>
+    <row r="33" xml:space="preserve">
+      <c r="A33" t="str">
+        <v>施設・設備</v>
+      </c>
+      <c r="B33" t="str">
+        <v>ゴミ・廃棄物の分別ルールは？</v>
+      </c>
+      <c r="C33" t="str" xml:space="preserve">
+        <v xml:space="preserve">①食品廃棄物：専用の緑色ボックスへ（毎日回収）
+②段ボール：プレス機で圧縮後、資源ゴミ置き場へ
+③プラスチック包材：黄色ボックスへ
+④一般ゴミ：黒袋で所定の場所へ。産業廃棄物は施設管理部（内線:300）の指示に従ってください。</v>
+      </c>
+      <c r="D33" t="str">
+        <v>ゴミ,廃棄,分別,リサイクル</v>
+      </c>
+    </row>
+    <row r="34" xml:space="preserve">
+      <c r="A34" t="str">
+        <v>施設・設備</v>
+      </c>
+      <c r="B34" t="str">
+        <v>冷蔵・冷凍設備の故障時の対応は？</v>
+      </c>
+      <c r="C34" t="str" xml:space="preserve">
+        <v xml:space="preserve">①設備管理部（内線:305）に即報告
+②冷蔵庫の場合は扉を開けないまま保温を維持
+③代替設備が必要な場合は管理責任者（内線:201）が手配
+④修理完了まで温度記録を通常より頻繁に（1時間ごと）実施してください。</v>
+      </c>
+      <c r="D34" t="str">
+        <v>設備故障,冷蔵,修理,対応</v>
+      </c>
+    </row>
+    <row r="35" xml:space="preserve">
+      <c r="A35" t="str">
+        <v>施設・設備</v>
+      </c>
+      <c r="B35" t="str">
+        <v>駐車場の利用ルールは？</v>
+      </c>
+      <c r="C35" t="str" xml:space="preserve">
+        <v xml:space="preserve">①従業員駐車場は事前登録制（総務部に申請）
+②配送車両は荷捌き場専用スペースを使用
+③来客駐車場は正門横3台分
+④無断駐車は警告のうえ移動させることがあります。</v>
+      </c>
+      <c r="D35" t="str">
+        <v>駐車場,駐車,登録</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D16"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D35"/>
   </ignoredErrors>
 </worksheet>
 </file>